--- a/frontend/public/templates/Template MOC.xlsx
+++ b/frontend/public/templates/Template MOC.xlsx
@@ -1,166 +1,755 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS ZENBOOK\Documents\1. College\Project\3. Pertamina\Template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{351DFCB1-732C-4710-8E13-3ACBF582C2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{453EFA3E-1C9E-4CEF-9871-7A0DC53F0281}"/>
   </bookViews>
   <sheets>
-    <sheet name="MOC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data_Dummy_MOC_Donggi_Matindok-" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="195">
+  <si>
+    <t>MOC_NUMBER</t>
+  </si>
+  <si>
+    <t>CHANGE_DESC</t>
+  </si>
+  <si>
+    <t>ISSUED_DATE</t>
+  </si>
+  <si>
+    <t>FIELD</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>MOC_OWNER</t>
+  </si>
+  <si>
+    <t>LAST_UPDATED</t>
+  </si>
+  <si>
+    <t>ONGOING_STEP</t>
+  </si>
+  <si>
+    <t>PIC</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>MOC-2026-001</t>
+  </si>
+  <si>
+    <t>Compressor Overhaul C-301 (Phase 2)</t>
+  </si>
+  <si>
+    <t>donggi</t>
+  </si>
+  <si>
+    <t>Agus Setiawan</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Fajar Nugroho</t>
+  </si>
+  <si>
+    <t>approved</t>
+  </si>
+  <si>
+    <t>MOC-2026-002</t>
+  </si>
+  <si>
+    <t>Control Room HVAC Upgrade (Phase 3)</t>
+  </si>
+  <si>
+    <t>Rian Hidayat</t>
+  </si>
+  <si>
+    <t>Archived</t>
+  </si>
+  <si>
+    <t>Wati Rahayu</t>
+  </si>
+  <si>
+    <t>cancelled</t>
+  </si>
+  <si>
+    <t>MOC-2026-003</t>
+  </si>
+  <si>
+    <t>Flare Knockout Drum Mod (Phase 3)</t>
+  </si>
+  <si>
+    <t>Dewi Lestari</t>
+  </si>
+  <si>
+    <t>Risk Assessment</t>
+  </si>
+  <si>
+    <t>Sinta Permata</t>
+  </si>
+  <si>
+    <t>on progress</t>
+  </si>
+  <si>
+    <t>MOC-2026-004</t>
+  </si>
+  <si>
+    <t>Compressor Overhaul C-301 (Phase 1)</t>
+  </si>
+  <si>
+    <t>matindok</t>
+  </si>
+  <si>
+    <t>MOC-2026-005</t>
+  </si>
+  <si>
+    <t>New Flare Tie-in Point (Phase 3)</t>
+  </si>
+  <si>
+    <t>Hendra Gunawan</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>MOC-2026-006</t>
+  </si>
+  <si>
+    <t>New Flare Tie-in Point (Phase 1)</t>
+  </si>
+  <si>
+    <t>PSSR</t>
+  </si>
+  <si>
+    <t>MOC-2026-007</t>
+  </si>
+  <si>
+    <t>Boiler B-201 Burner Change (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-008</t>
+  </si>
+  <si>
+    <t>Metering Station Upgrade (Phase 3)</t>
+  </si>
+  <si>
+    <t>Rini Astuti</t>
+  </si>
+  <si>
+    <t>MOC-2026-009</t>
+  </si>
+  <si>
+    <t>Lube Oil System Change (Phase 1)</t>
+  </si>
+  <si>
+    <t>Siti Aminah</t>
+  </si>
+  <si>
+    <t>MOC-2026-010</t>
+  </si>
+  <si>
+    <t>Gas Turbine Filter Replace (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-011</t>
+  </si>
+  <si>
+    <t>Budi Santoso</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>MOC-2026-012</t>
+  </si>
+  <si>
+    <t>Generator G-400 Repair (Phase 3)</t>
+  </si>
+  <si>
+    <t>Engineering Design</t>
+  </si>
+  <si>
+    <t>Andi Wirawan</t>
+  </si>
+  <si>
+    <t>MOC-2026-013</t>
+  </si>
+  <si>
+    <t>Tank T-100 Maintenance (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-014</t>
+  </si>
+  <si>
+    <t>MOC-2026-015</t>
+  </si>
+  <si>
+    <t>Eko Prabowo</t>
+  </si>
+  <si>
+    <t>MOC-2026-016</t>
+  </si>
+  <si>
+    <t>MOC-2026-017</t>
+  </si>
+  <si>
+    <t>Condensate Line Repair (Phase 2)</t>
+  </si>
+  <si>
+    <t>Dian Sastro</t>
+  </si>
+  <si>
+    <t>MOC-2026-018</t>
+  </si>
+  <si>
+    <t>MOC-2026-019</t>
+  </si>
+  <si>
+    <t>Water Treatment Bypass (Phase 2)</t>
+  </si>
+  <si>
+    <t>4a</t>
+  </si>
+  <si>
+    <t>MOC-2026-020</t>
+  </si>
+  <si>
+    <t>Pipeline Rerouting Area A (Phase 2)</t>
+  </si>
+  <si>
+    <t>Joko Anwar</t>
+  </si>
+  <si>
+    <t>MOC-2026-021</t>
+  </si>
+  <si>
+    <t>Pipeline Rerouting Area A (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-022</t>
+  </si>
+  <si>
+    <t>Pump P-205 Upgrade (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-023</t>
+  </si>
+  <si>
+    <t>4b</t>
+  </si>
+  <si>
+    <t>MOC-2026-024</t>
+  </si>
+  <si>
+    <t>Vessel V-502 Inspection (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-025</t>
+  </si>
+  <si>
+    <t>MOC-2026-026</t>
+  </si>
+  <si>
+    <t>Cooling Tower Fan Mod (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-027</t>
+  </si>
+  <si>
+    <t>Lube Oil System Change (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-028</t>
+  </si>
+  <si>
+    <t>MOC-2026-029</t>
+  </si>
+  <si>
+    <t>Condensate Line Repair (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-030</t>
+  </si>
+  <si>
+    <t>Chemical Injection Skid (Phase 2)</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>MOC-2026-031</t>
+  </si>
+  <si>
+    <t>Valve V-102 Replacement (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-032</t>
+  </si>
+  <si>
+    <t>Chemical Injection Skid (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-033</t>
+  </si>
+  <si>
+    <t>MOC-2026-034</t>
+  </si>
+  <si>
+    <t>Scrubber Internals Mod (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-035</t>
+  </si>
+  <si>
+    <t>Generator G-400 Repair (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-036</t>
+  </si>
+  <si>
+    <t>Separator S-101 Logic Update (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-037</t>
+  </si>
+  <si>
+    <t>Firewater Pump Testing (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-038</t>
+  </si>
+  <si>
+    <t>MOC-2026-039</t>
+  </si>
+  <si>
+    <t>Pump P-205 Upgrade (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-040</t>
+  </si>
+  <si>
+    <t>MOC-2026-041</t>
+  </si>
+  <si>
+    <t>Instrument Air Calibration (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-042</t>
+  </si>
+  <si>
+    <t>Boiler B-201 Burner Change (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-043</t>
+  </si>
+  <si>
+    <t>MOC-2026-044</t>
+  </si>
+  <si>
+    <t>MOC-2026-045</t>
+  </si>
+  <si>
+    <t>MOC-2026-046</t>
+  </si>
+  <si>
+    <t>Wellhead Panel Mod (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-047</t>
+  </si>
+  <si>
+    <t>MOC-2026-048</t>
+  </si>
+  <si>
+    <t>Gas Turbine Filter Replace (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-049</t>
+  </si>
+  <si>
+    <t>Heat Exchanger Cleaning (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-050</t>
+  </si>
+  <si>
+    <t>Wellhead Panel Mod (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-051</t>
+  </si>
+  <si>
+    <t>MOC-2026-052</t>
+  </si>
+  <si>
+    <t>Pump P-205 Upgrade (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-053</t>
+  </si>
+  <si>
+    <t>Lube Oil System Change (Phase 3)</t>
+  </si>
+  <si>
+    <t>Management Approval</t>
+  </si>
+  <si>
+    <t>MOC-2026-054</t>
+  </si>
+  <si>
+    <t>MOC-2026-055</t>
+  </si>
+  <si>
+    <t>MOC-2026-056</t>
+  </si>
+  <si>
+    <t>Gas Turbine Filter Replace (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-057</t>
+  </si>
+  <si>
+    <t>MOC-2026-058</t>
+  </si>
+  <si>
+    <t>MOC-2026-059</t>
+  </si>
+  <si>
+    <t>MOC-2026-060</t>
+  </si>
+  <si>
+    <t>Instrument Air Calibration (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-061</t>
+  </si>
+  <si>
+    <t>Vessel V-502 Inspection (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-062</t>
+  </si>
+  <si>
+    <t>Flare Knockout Drum Mod (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-063</t>
+  </si>
+  <si>
+    <t>MOC-2026-064</t>
+  </si>
+  <si>
+    <t>Control Room HVAC Upgrade (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-065</t>
+  </si>
+  <si>
+    <t>Generator G-400 Repair (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-066</t>
+  </si>
+  <si>
+    <t>Flare Knockout Drum Mod (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-067</t>
+  </si>
+  <si>
+    <t>Heat Exchanger Cleaning (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-068</t>
+  </si>
+  <si>
+    <t>Cooling Tower Fan Mod (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-069</t>
+  </si>
+  <si>
+    <t>DCS System Modification (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-070</t>
+  </si>
+  <si>
+    <t>Instrument Air Calibration (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-071</t>
+  </si>
+  <si>
+    <t>MOC-2026-072</t>
+  </si>
+  <si>
+    <t>MOC-2026-073</t>
+  </si>
+  <si>
+    <t>MOC-2026-074</t>
+  </si>
+  <si>
+    <t>MOC-2026-075</t>
+  </si>
+  <si>
+    <t>MOC-2026-076</t>
+  </si>
+  <si>
+    <t>Valve V-102 Replacement (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-077</t>
+  </si>
+  <si>
+    <t>MOC-2026-078</t>
+  </si>
+  <si>
+    <t>MOC-2026-079</t>
+  </si>
+  <si>
+    <t>MOC-2026-080</t>
+  </si>
+  <si>
+    <t>Vessel V-502 Inspection (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-081</t>
+  </si>
+  <si>
+    <t>MOC-2026-082</t>
+  </si>
+  <si>
+    <t>MOC-2026-083</t>
+  </si>
+  <si>
+    <t>MOC-2026-084</t>
+  </si>
+  <si>
+    <t>MOC-2026-085</t>
+  </si>
+  <si>
+    <t>New Flare Tie-in Point (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-086</t>
+  </si>
+  <si>
+    <t>MOC-2026-087</t>
+  </si>
+  <si>
+    <t>MOC-2026-088</t>
+  </si>
+  <si>
+    <t>MOC-2026-089</t>
+  </si>
+  <si>
+    <t>MOC-2026-090</t>
+  </si>
+  <si>
+    <t>MOC-2026-091</t>
+  </si>
+  <si>
+    <t>Cooling Tower Fan Mod (Phase 1)</t>
+  </si>
+  <si>
+    <t>MOC-2026-092</t>
+  </si>
+  <si>
+    <t>Valve V-102 Replacement (Phase 2)</t>
+  </si>
+  <si>
+    <t>MOC-2026-093</t>
+  </si>
+  <si>
+    <t>MOC-2026-094</t>
+  </si>
+  <si>
+    <t>MOC-2026-095</t>
+  </si>
+  <si>
+    <t>DCS System Modification (Phase 3)</t>
+  </si>
+  <si>
+    <t>MOC-2026-096</t>
+  </si>
+  <si>
+    <t>MOC-2026-097</t>
+  </si>
+  <si>
+    <t>MOC-2026-098</t>
+  </si>
+  <si>
+    <t>MOC-2026-099</t>
+  </si>
+  <si>
+    <t>MOC-2026-100</t>
+  </si>
+  <si>
+    <t>Boiler B-201 Burner Change (Phase 1)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Aptos Display"/>
       <family val="2"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="major"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FF9C5700"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -207,19 +796,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999816888943144"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -230,19 +819,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -253,19 +842,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999816888943144"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.3999755851924192"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -276,19 +865,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999938962981048"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.3999755851924192"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -299,19 +888,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.5999938962981048"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.3999755851924192"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -322,30 +911,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00008A45"/>
-        <bgColor rgb="00008A45"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -376,7 +959,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.3999755851924192"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -460,185 +1043,109 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00007038"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00007038"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Title" xfId="1" builtinId="15"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19"/>
-    <cellStyle name="Good" xfId="6" builtinId="26"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
-    <cellStyle name="Input" xfId="9" builtinId="20"/>
-    <cellStyle name="Output" xfId="10" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="Note" xfId="15" builtinId="10"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53"/>
-    <cellStyle name="Total" xfId="17" builtinId="25"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -958,76 +1465,3240 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2226355-4E22-4C93-96EF-A740A27C62F8}">
+  <dimension ref="A1:J101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>MOC_NUMBER</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>CHANGE_DESC</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>ISSUED_DATE</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>FIELD</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>MOC_OWNER</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>LAST_UPDATED</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>ONGOING_STEP</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>PIC</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1">
+        <v>45890</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45919</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45714</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1">
+        <v>45736</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45762</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45777</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45835</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45851</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45984</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45992</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45743</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45748</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45684</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45708</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45831</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45852</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45709</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1">
+        <v>45797</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45798</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="1">
+        <v>45825</v>
+      </c>
+      <c r="H12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45976</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1">
+        <v>45987</v>
+      </c>
+      <c r="H13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45718</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45735</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="1">
+        <v>45759</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45900</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45929</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45993</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45900</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1">
+        <v>45919</v>
+      </c>
+      <c r="H18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45786</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45804</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45791</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45818</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45813</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45819</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" t="s">
+        <v>60</v>
+      </c>
+      <c r="J21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45698</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45710</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45838</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45853</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45974</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="1">
+        <v>45990</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45747</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1">
+        <v>45764</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" t="s">
+        <v>60</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45953</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45975</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="1">
+        <v>45916</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="1">
+        <v>45924</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="1">
+        <v>45878</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="1">
+        <v>45905</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>55</v>
+      </c>
+      <c r="J28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1">
+        <v>45737</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45757</v>
+      </c>
+      <c r="H29" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="1">
+        <v>45733</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45742</v>
+      </c>
+      <c r="H30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="1">
+        <v>45823</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="1">
+        <v>45831</v>
+      </c>
+      <c r="H31" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1">
+        <v>45794</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" t="s">
+        <v>60</v>
+      </c>
+      <c r="J32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="1">
+        <v>45902</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1">
+        <v>45918</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>55</v>
+      </c>
+      <c r="J33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" s="1">
+        <v>45955</v>
+      </c>
+      <c r="H34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="1">
+        <v>45663</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="1">
+        <v>45671</v>
+      </c>
+      <c r="H35" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" t="s">
+        <v>55</v>
+      </c>
+      <c r="J35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46014</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>50</v>
+      </c>
+      <c r="G36" s="1">
+        <v>46033</v>
+      </c>
+      <c r="H36" t="s">
+        <v>90</v>
+      </c>
+      <c r="I36" t="s">
+        <v>60</v>
+      </c>
+      <c r="J36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="1">
+        <v>45974</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="1">
+        <v>45983</v>
+      </c>
+      <c r="H37" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" s="1">
+        <v>45762</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="1">
+        <v>45777</v>
+      </c>
+      <c r="H38" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s">
+        <v>55</v>
+      </c>
+      <c r="J38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="1">
+        <v>45741</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="1">
+        <v>45761</v>
+      </c>
+      <c r="H39" t="s">
+        <v>51</v>
+      </c>
+      <c r="I39" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="1">
+        <v>45689</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40" t="s">
+        <v>46</v>
+      </c>
+      <c r="G40" s="1">
+        <v>45707</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="1">
+        <v>45769</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="1">
+        <v>45783</v>
+      </c>
+      <c r="H41" t="s">
+        <v>54</v>
+      </c>
+      <c r="I41" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="1">
+        <v>45748</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="1">
+        <v>45754</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="1">
+        <v>45847</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="1">
+        <v>45858</v>
+      </c>
+      <c r="H43" t="s">
+        <v>90</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="1">
+        <v>45963</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="1">
+        <v>45969</v>
+      </c>
+      <c r="H44" t="s">
+        <v>90</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="1">
+        <v>45974</v>
+      </c>
+      <c r="D45" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="1">
+        <v>46002</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="1">
+        <v>45752</v>
+      </c>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="1">
+        <v>45767</v>
+      </c>
+      <c r="H46" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="1">
+        <v>45929</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G47" s="1">
+        <v>45940</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" t="s">
+        <v>55</v>
+      </c>
+      <c r="J47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="1">
+        <v>45770</v>
+      </c>
+      <c r="D48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>50</v>
+      </c>
+      <c r="G48" s="1">
+        <v>45785</v>
+      </c>
+      <c r="H48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" t="s">
+        <v>64</v>
+      </c>
+      <c r="J48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46011</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>71</v>
+      </c>
+      <c r="G49" s="1">
+        <v>46026</v>
+      </c>
+      <c r="H49" t="s">
+        <v>51</v>
+      </c>
+      <c r="I49" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="1">
+        <v>45777</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50">
+        <v>7</v>
+      </c>
+      <c r="F50" t="s">
+        <v>50</v>
+      </c>
+      <c r="G50" s="1">
+        <v>45794</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50" t="s">
+        <v>43</v>
+      </c>
+      <c r="J50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="1">
+        <v>45708</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="1">
+        <v>45738</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="1">
+        <v>45941</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="1">
+        <v>45967</v>
+      </c>
+      <c r="H52" t="s">
+        <v>90</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C53" s="1">
+        <v>45909</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>50</v>
+      </c>
+      <c r="G53" s="1">
+        <v>45933</v>
+      </c>
+      <c r="H53" t="s">
+        <v>51</v>
+      </c>
+      <c r="I53" t="s">
+        <v>43</v>
+      </c>
+      <c r="J53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="1">
+        <v>45678</v>
+      </c>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54">
+        <v>5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>46</v>
+      </c>
+      <c r="G54" s="1">
+        <v>45695</v>
+      </c>
+      <c r="H54" t="s">
+        <v>129</v>
+      </c>
+      <c r="I54" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="1">
+        <v>45966</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+      <c r="F55" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="1">
+        <v>45992</v>
+      </c>
+      <c r="H55" t="s">
+        <v>90</v>
+      </c>
+      <c r="I55" t="s">
+        <v>55</v>
+      </c>
+      <c r="J55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="1">
+        <v>45965</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="1">
+        <v>45979</v>
+      </c>
+      <c r="H56" t="s">
+        <v>129</v>
+      </c>
+      <c r="I56" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>132</v>
+      </c>
+      <c r="B57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="1">
+        <v>45763</v>
+      </c>
+      <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>50</v>
+      </c>
+      <c r="G57" s="1">
+        <v>45788</v>
+      </c>
+      <c r="H57" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" t="s">
+        <v>55</v>
+      </c>
+      <c r="J57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="1">
+        <v>45953</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" s="1">
+        <v>45965</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="1">
+        <v>45943</v>
+      </c>
+      <c r="H59" t="s">
+        <v>38</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" s="1">
+        <v>45729</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" s="1">
+        <v>45716</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="s">
+        <v>43</v>
+      </c>
+      <c r="J61" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="1">
+        <v>45741</v>
+      </c>
+      <c r="D62" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="1">
+        <v>45765</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" t="s">
+        <v>64</v>
+      </c>
+      <c r="J62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" s="1">
+        <v>45837</v>
+      </c>
+      <c r="D63" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1">
+        <v>45855</v>
+      </c>
+      <c r="H63" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>60</v>
+      </c>
+      <c r="J63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>143</v>
+      </c>
+      <c r="B64" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" s="1">
+        <v>45675</v>
+      </c>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64">
+        <v>10</v>
+      </c>
+      <c r="F64" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="1">
+        <v>45700</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" s="1">
+        <v>45882</v>
+      </c>
+      <c r="D65" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="1">
+        <v>45891</v>
+      </c>
+      <c r="H65" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>64</v>
+      </c>
+      <c r="J65" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="1">
+        <v>45697</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66" s="1">
+        <v>45714</v>
+      </c>
+      <c r="H66" t="s">
+        <v>51</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" t="s">
+        <v>149</v>
+      </c>
+      <c r="C67" s="1">
+        <v>45796</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67">
+        <v>10</v>
+      </c>
+      <c r="F67" t="s">
+        <v>50</v>
+      </c>
+      <c r="G67" s="1">
+        <v>45802</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" t="s">
+        <v>64</v>
+      </c>
+      <c r="J67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" t="s">
+        <v>151</v>
+      </c>
+      <c r="C68" s="1">
+        <v>45836</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="1">
+        <v>45859</v>
+      </c>
+      <c r="H68" t="s">
+        <v>51</v>
+      </c>
+      <c r="I68" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="1">
+        <v>45923</v>
+      </c>
+      <c r="D69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" t="s">
+        <v>68</v>
+      </c>
+      <c r="F69" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="1">
+        <v>45947</v>
+      </c>
+      <c r="H69" t="s">
+        <v>90</v>
+      </c>
+      <c r="I69" t="s">
+        <v>43</v>
+      </c>
+      <c r="J69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" t="s">
+        <v>155</v>
+      </c>
+      <c r="C70" s="1">
+        <v>45999</v>
+      </c>
+      <c r="D70" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70">
+        <v>10</v>
+      </c>
+      <c r="F70" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="1">
+        <v>46013</v>
+      </c>
+      <c r="H70" t="s">
+        <v>51</v>
+      </c>
+      <c r="I70" t="s">
+        <v>60</v>
+      </c>
+      <c r="J70" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>156</v>
+      </c>
+      <c r="B71" t="s">
+        <v>157</v>
+      </c>
+      <c r="C71" s="1">
+        <v>45733</v>
+      </c>
+      <c r="D71" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71">
+        <v>9</v>
+      </c>
+      <c r="F71" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H71" t="s">
+        <v>90</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="1">
+        <v>45982</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72">
+        <v>10</v>
+      </c>
+      <c r="F72" t="s">
+        <v>71</v>
+      </c>
+      <c r="G72" s="1">
+        <v>45994</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" s="1">
+        <v>45983</v>
+      </c>
+      <c r="D73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73">
+        <v>10</v>
+      </c>
+      <c r="F73" t="s">
+        <v>71</v>
+      </c>
+      <c r="G73" s="1">
+        <v>46006</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" t="s">
+        <v>55</v>
+      </c>
+      <c r="J73" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>160</v>
+      </c>
+      <c r="B74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C74" s="1">
+        <v>45945</v>
+      </c>
+      <c r="D74" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74">
+        <v>7</v>
+      </c>
+      <c r="F74" t="s">
+        <v>34</v>
+      </c>
+      <c r="G74" s="1">
+        <v>45963</v>
+      </c>
+      <c r="H74" t="s">
+        <v>54</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>161</v>
+      </c>
+      <c r="B75" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75" s="1">
+        <v>45730</v>
+      </c>
+      <c r="D75" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75">
+        <v>8</v>
+      </c>
+      <c r="F75" t="s">
+        <v>71</v>
+      </c>
+      <c r="G75" s="1">
+        <v>45745</v>
+      </c>
+      <c r="H75" t="s">
+        <v>54</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="1">
+        <v>45722</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76" t="s">
+        <v>60</v>
+      </c>
+      <c r="J76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46022</v>
+      </c>
+      <c r="D77" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" t="s">
+        <v>68</v>
+      </c>
+      <c r="F77" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="1">
+        <v>46051</v>
+      </c>
+      <c r="H77" t="s">
+        <v>129</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>165</v>
+      </c>
+      <c r="B78" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" s="1">
+        <v>45708</v>
+      </c>
+      <c r="D78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78">
+        <v>10</v>
+      </c>
+      <c r="F78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H78" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" t="s">
+        <v>87</v>
+      </c>
+      <c r="C79" s="1">
+        <v>45949</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79">
+        <v>8</v>
+      </c>
+      <c r="F79" t="s">
+        <v>50</v>
+      </c>
+      <c r="G79" s="1">
+        <v>45955</v>
+      </c>
+      <c r="H79" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" t="s">
+        <v>75</v>
+      </c>
+      <c r="C80" s="1">
+        <v>45820</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+      <c r="F80" t="s">
+        <v>34</v>
+      </c>
+      <c r="G80" s="1">
+        <v>45825</v>
+      </c>
+      <c r="H80" t="s">
+        <v>51</v>
+      </c>
+      <c r="I80" t="s">
+        <v>64</v>
+      </c>
+      <c r="J80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>168</v>
+      </c>
+      <c r="B81" t="s">
+        <v>169</v>
+      </c>
+      <c r="C81" s="1">
+        <v>45704</v>
+      </c>
+      <c r="D81" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81">
+        <v>10</v>
+      </c>
+      <c r="F81" t="s">
+        <v>34</v>
+      </c>
+      <c r="G81" s="1">
+        <v>45720</v>
+      </c>
+      <c r="H81" t="s">
+        <v>51</v>
+      </c>
+      <c r="I81" t="s">
+        <v>27</v>
+      </c>
+      <c r="J81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>170</v>
+      </c>
+      <c r="B82" t="s">
+        <v>147</v>
+      </c>
+      <c r="C82" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82">
+        <v>5</v>
+      </c>
+      <c r="F82" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45986</v>
+      </c>
+      <c r="H82" t="s">
+        <v>54</v>
+      </c>
+      <c r="I82" t="s">
+        <v>60</v>
+      </c>
+      <c r="J82" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" s="1">
+        <v>45987</v>
+      </c>
+      <c r="D83" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="1">
+        <v>46012</v>
+      </c>
+      <c r="H83" t="s">
+        <v>38</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>172</v>
+      </c>
+      <c r="B84" t="s">
+        <v>164</v>
+      </c>
+      <c r="C84" s="1">
+        <v>45891</v>
+      </c>
+      <c r="D84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E84">
+        <v>10</v>
+      </c>
+      <c r="F84" t="s">
+        <v>46</v>
+      </c>
+      <c r="G84" s="1">
+        <v>45911</v>
+      </c>
+      <c r="H84" t="s">
+        <v>51</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" t="s">
+        <v>63</v>
+      </c>
+      <c r="C85" s="1">
+        <v>45947</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>46</v>
+      </c>
+      <c r="G85" s="1">
+        <v>45952</v>
+      </c>
+      <c r="H85" t="s">
+        <v>38</v>
+      </c>
+      <c r="I85" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>174</v>
+      </c>
+      <c r="B86" t="s">
+        <v>175</v>
+      </c>
+      <c r="C86" s="1">
+        <v>45740</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
+        <v>46</v>
+      </c>
+      <c r="G86" s="1">
+        <v>45766</v>
+      </c>
+      <c r="H86" t="s">
+        <v>26</v>
+      </c>
+      <c r="I86" t="s">
+        <v>55</v>
+      </c>
+      <c r="J86" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" t="s">
+        <v>169</v>
+      </c>
+      <c r="C87" s="1">
+        <v>45939</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87">
+        <v>10</v>
+      </c>
+      <c r="F87" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" s="1">
+        <v>45954</v>
+      </c>
+      <c r="H87" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" t="s">
+        <v>64</v>
+      </c>
+      <c r="J87" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" s="1">
+        <v>45756</v>
+      </c>
+      <c r="D88" t="s">
+        <v>31</v>
+      </c>
+      <c r="E88">
+        <v>10</v>
+      </c>
+      <c r="F88" t="s">
+        <v>71</v>
+      </c>
+      <c r="G88" s="1">
+        <v>45764</v>
+      </c>
+      <c r="H88" t="s">
+        <v>51</v>
+      </c>
+      <c r="I88" t="s">
+        <v>27</v>
+      </c>
+      <c r="J88" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" t="s">
+        <v>121</v>
+      </c>
+      <c r="C89" s="1">
+        <v>45676</v>
+      </c>
+      <c r="D89" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89">
+        <v>7</v>
+      </c>
+      <c r="F89" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="1">
+        <v>45702</v>
+      </c>
+      <c r="H89" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" t="s">
+        <v>43</v>
+      </c>
+      <c r="J89" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>179</v>
+      </c>
+      <c r="B90" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90" s="1">
+        <v>45939</v>
+      </c>
+      <c r="D90" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" t="s">
+        <v>77</v>
+      </c>
+      <c r="F90" t="s">
+        <v>50</v>
+      </c>
+      <c r="G90" s="1">
+        <v>45964</v>
+      </c>
+      <c r="H90" t="s">
+        <v>54</v>
+      </c>
+      <c r="I90" t="s">
+        <v>55</v>
+      </c>
+      <c r="J90" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" s="1">
+        <v>45929</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91" t="s">
+        <v>50</v>
+      </c>
+      <c r="G91" s="1">
+        <v>45942</v>
+      </c>
+      <c r="H91" t="s">
+        <v>26</v>
+      </c>
+      <c r="I91" t="s">
+        <v>15</v>
+      </c>
+      <c r="J91" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>181</v>
+      </c>
+      <c r="B92" t="s">
+        <v>182</v>
+      </c>
+      <c r="C92" s="1">
+        <v>45846</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92">
+        <v>9</v>
+      </c>
+      <c r="F92" t="s">
+        <v>34</v>
+      </c>
+      <c r="G92" s="1">
+        <v>45868</v>
+      </c>
+      <c r="H92" t="s">
+        <v>26</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" s="1">
+        <v>45771</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93">
+        <v>9</v>
+      </c>
+      <c r="F93" t="s">
+        <v>50</v>
+      </c>
+      <c r="G93" s="1">
+        <v>45798</v>
+      </c>
+      <c r="H93" t="s">
+        <v>38</v>
+      </c>
+      <c r="I93" t="s">
+        <v>55</v>
+      </c>
+      <c r="J93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>185</v>
+      </c>
+      <c r="B94" t="s">
+        <v>184</v>
+      </c>
+      <c r="C94" s="1">
+        <v>45738</v>
+      </c>
+      <c r="D94" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94">
+        <v>6</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="1">
+        <v>45768</v>
+      </c>
+      <c r="H94" t="s">
+        <v>38</v>
+      </c>
+      <c r="I94" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>186</v>
+      </c>
+      <c r="B95" t="s">
+        <v>82</v>
+      </c>
+      <c r="C95" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D95" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95">
+        <v>4</v>
+      </c>
+      <c r="F95" t="s">
+        <v>71</v>
+      </c>
+      <c r="G95" s="1">
+        <v>45814</v>
+      </c>
+      <c r="H95" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" t="s">
+        <v>43</v>
+      </c>
+      <c r="J95" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>187</v>
+      </c>
+      <c r="B96" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" s="1">
+        <v>45765</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96">
+        <v>8</v>
+      </c>
+      <c r="F96" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="1">
+        <v>45772</v>
+      </c>
+      <c r="H96" t="s">
+        <v>54</v>
+      </c>
+      <c r="I96" t="s">
+        <v>60</v>
+      </c>
+      <c r="J96" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>189</v>
+      </c>
+      <c r="B97" t="s">
+        <v>84</v>
+      </c>
+      <c r="C97" s="1">
+        <v>45978</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" t="s">
+        <v>77</v>
+      </c>
+      <c r="F97" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" s="1">
+        <v>45999</v>
+      </c>
+      <c r="H97" t="s">
+        <v>129</v>
+      </c>
+      <c r="I97" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>190</v>
+      </c>
+      <c r="B98" t="s">
+        <v>126</v>
+      </c>
+      <c r="C98" s="1">
+        <v>45676</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" t="s">
+        <v>68</v>
+      </c>
+      <c r="F98" t="s">
+        <v>50</v>
+      </c>
+      <c r="G98" s="1">
+        <v>45691</v>
+      </c>
+      <c r="H98" t="s">
+        <v>38</v>
+      </c>
+      <c r="I98" t="s">
+        <v>64</v>
+      </c>
+      <c r="J98" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>191</v>
+      </c>
+      <c r="B99" t="s">
+        <v>188</v>
+      </c>
+      <c r="C99" s="1">
+        <v>46005</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99">
+        <v>10</v>
+      </c>
+      <c r="F99" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="1">
+        <v>46024</v>
+      </c>
+      <c r="H99" t="s">
+        <v>51</v>
+      </c>
+      <c r="I99" t="s">
+        <v>60</v>
+      </c>
+      <c r="J99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" t="s">
+        <v>89</v>
+      </c>
+      <c r="C100" s="1">
+        <v>45735</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100">
+        <v>10</v>
+      </c>
+      <c r="F100" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" s="1">
+        <v>45759</v>
+      </c>
+      <c r="H100" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" t="s">
+        <v>64</v>
+      </c>
+      <c r="J100" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>193</v>
+      </c>
+      <c r="B101" t="s">
+        <v>194</v>
+      </c>
+      <c r="C101" s="1">
+        <v>45659</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101">
+        <v>10</v>
+      </c>
+      <c r="F101" t="s">
+        <v>71</v>
+      </c>
+      <c r="G101" s="1">
+        <v>45681</v>
+      </c>
+      <c r="H101" t="s">
+        <v>51</v>
+      </c>
+      <c r="I101" t="s">
+        <v>27</v>
+      </c>
+      <c r="J101" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
